--- a/data/capstone-website-visits-by-weekday.xlsx
+++ b/data/capstone-website-visits-by-weekday.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="visits" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codebook" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PriorYear" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,8 +423,8 @@
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -522,9 +523,9 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="67" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -592,7 +593,7 @@
   <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -640,4 +641,104 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>weekday</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>prior_year_share</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.163</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.157</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.145</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.116</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.109</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>